--- a/StructureDefinition-ng-tb-questionnaire.xlsx
+++ b/StructureDefinition-ng-tb-questionnaire.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T15:57:17+01:00</t>
+    <t>2026-08-18T16:47:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
